--- a/data/trans_bre/P32A-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,0</t>
+          <t>-2,64; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,14</t>
+          <t>-4,8; 0,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,15</t>
+          <t>-1,89; 3,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 13,49</t>
+          <t>0,35; 12,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,13</t>
+          <t>-100,0; 82,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,01</t>
+          <t>-1,6; 1,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -0,81</t>
+          <t>-4,36; -0,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,3</t>
+          <t>-3,96; 0,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 2,54</t>
+          <t>-1,96; 2,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,37</t>
+          <t>-100,0; 13,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,11</t>
+          <t>-100,0; 57,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 1,52</t>
+          <t>-1,71; 1,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -0,97</t>
+          <t>-4,86; -0,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,3</t>
+          <t>-3,01; 0,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,55</t>
+          <t>-1,3; 2,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 486,07</t>
+          <t>-100,0; 574,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 3,3</t>
+          <t>-100,0; -11,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,05</t>
+          <t>-100,0; 81,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 3569,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,0</t>
+          <t>-2,3; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,14</t>
+          <t>-4,66; -0,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,42</t>
+          <t>-3,45; 0,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,27</t>
+          <t>-3,44; 0,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 137,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 114,27</t>
+          <t>-100,0; 146,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-97,33; 74,69</t>
+          <t>-97,52; 108,84</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; -1,0</t>
+          <t>-6,39; -0,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 9,25</t>
+          <t>-0,22; 10,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 6,51</t>
+          <t>-1,9; 7,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 1,49</t>
+          <t>-4,24; 1,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 695,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-84,0; 81,72</t>
+          <t>-82,84; 81,61</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,21; -0,61</t>
+          <t>-5,23; -0,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 5,27</t>
+          <t>-2,64; 5,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -0,01</t>
+          <t>-4,5; -0,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,07</t>
+          <t>-100,0; 6,93</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,0</t>
+          <t>-6,77; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 0,0</t>
+          <t>-12,66; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,84</t>
+          <t>0,0; 16,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 5,45</t>
+          <t>-3,47; 5,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,16</t>
+          <t>-1,32; -0,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,69</t>
+          <t>-2,6; -0,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,33</t>
+          <t>-1,63; 0,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,77</t>
+          <t>-1,49; 0,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,29; -2,0</t>
+          <t>-93,63; 7,88</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,49; -29,94</t>
+          <t>-86,29; -24,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 24,37</t>
+          <t>-66,2; 21,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 53,64</t>
+          <t>-66,61; 50,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32A-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,2</t>
+          <t>7,07</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 0,46</t>
+          <t>-4,81; 0,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,32</t>
+          <t>-1,89; 3,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 12,58</t>
+          <t>2,0; 16,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,84</t>
+          <t>-100,0; 58,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>136,79%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,0</t>
+          <t>-1,6; 1,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -0,96</t>
+          <t>-4,35; -0,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 0,15</t>
+          <t>-4,32; 0,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 2,58</t>
+          <t>-0,51; 3,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,04</t>
+          <t>-100,0; 0,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 57,42</t>
+          <t>-100,0; 44,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,29</t>
+          <t>-1,78; 1,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; -0,96</t>
+          <t>-4,72; -0,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,32</t>
+          <t>-2,91; 0,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 2,48</t>
+          <t>-1,59; 2,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 574,68</t>
+          <t>-100,0; 376,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,86</t>
+          <t>-100,0; 7,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 81,12</t>
+          <t>-100,0; 68,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-64,04%</t>
+          <t>-57,26%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,0</t>
+          <t>-2,33; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -0,25</t>
+          <t>-4,14; -0,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 0,52</t>
+          <t>-3,36; 0,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,25</t>
+          <t>-3,41; 0,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,63</t>
+          <t>-100,0; 125,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-97,52; 108,84</t>
+          <t>-96,4; 74,48</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,58</t>
+          <t>-1,36</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-42,25%</t>
+          <t>-39,2%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -0,99</t>
+          <t>-6,83; -0,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 10,2</t>
+          <t>-0,97; 8,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 7,0</t>
+          <t>-1,87; 6,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,33</t>
+          <t>-4,17; 1,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 695,81</t>
+          <t>-100,0; 682,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,84; 81,61</t>
+          <t>-84,06; 98,59</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,89</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-80,52%</t>
+          <t>-34,57%</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,6</t>
+          <t>-5,15; -0,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 5,07</t>
+          <t>-2,71; 5,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,5; -0,02</t>
+          <t>-3,24; 1,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,93</t>
+          <t>-86,98; 208,53</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-11,51%</t>
+          <t>61,33%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 0,0</t>
+          <t>-6,89; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 0,0</t>
+          <t>-12,78; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,48</t>
+          <t>0,0; 15,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,01</t>
+          <t>-2,27; 10,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-22,18%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,32; -0,06</t>
+          <t>-1,32; -0,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,63</t>
+          <t>-2,7; -0,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,33</t>
+          <t>-1,46; 0,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,71</t>
+          <t>-0,75; 1,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-93,63; 7,88</t>
+          <t>-92,11; 2,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-86,29; -24,03</t>
+          <t>-86,71; -28,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,2; 21,08</t>
+          <t>-63,82; 27,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 50,79</t>
+          <t>-36,37; 115,8</t>
         </is>
       </c>
     </row>
